--- a/public/exports-from-60-with-coowners/29189730.xlsx
+++ b/public/exports-from-60-with-coowners/29189730.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256418</t>
+          <t xml:space="preserve">311256422</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654759</t>
+          <t xml:space="preserve">311654760</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706715</t>
+          <t xml:space="preserve">311706717</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706728</t>
+          <t xml:space="preserve">311706741</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706728</t>
+          <t xml:space="preserve">311706741</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706728</t>
+          <t xml:space="preserve">311706741</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706895</t>
+          <t xml:space="preserve">311706919</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706895</t>
+          <t xml:space="preserve">311706919</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -16939,12 +16939,12 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710301</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -17164,12 +17164,12 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710293</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M229" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189730.xlsx
+++ b/public/exports-from-60-with-coowners/29189730.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256422</t>
+          <t xml:space="preserve">311256418</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13039,12 +13039,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706451</t>
+          <t xml:space="preserve">311706452</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706717</t>
+          <t xml:space="preserve">311706715</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706741</t>
+          <t xml:space="preserve">311706979</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706741</t>
+          <t xml:space="preserve">311706979</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706741</t>
+          <t xml:space="preserve">311706979</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706919</t>
+          <t xml:space="preserve">311706982</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706919</t>
+          <t xml:space="preserve">311706982</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706709</t>
+          <t xml:space="preserve">311706968</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706709</t>
+          <t xml:space="preserve">311706968</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -16864,12 +16864,12 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710303</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -16939,12 +16939,12 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710301</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -17014,12 +17014,12 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710304</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -17089,12 +17089,12 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710306</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17164,12 +17164,12 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710293</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189730.xlsx
+++ b/public/exports-from-60-with-coowners/29189730.xlsx
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654760</t>
+          <t xml:space="preserve">311654759</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13039,12 +13039,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706982</t>
+          <t xml:space="preserve">311706895</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706982</t>
+          <t xml:space="preserve">311706895</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706968</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706968</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -16864,12 +16864,12 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710303</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -17014,12 +17014,12 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710304</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -17089,12 +17089,12 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710306</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M228" t="inlineStr">
